--- a/حركات الأسنان والبصريات - مصححة نهائيا/حركات الشركات للبصريات - مصححة/WAB_Transactions_Optics.xlsx
+++ b/حركات الأسنان والبصريات - مصححة نهائيا/حركات الشركات للبصريات - مصححة/WAB_Transactions_Optics.xlsx
@@ -1,23 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC461690-DDC8-4585-AB9C-890FE2B5419D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="البصريات" state="visible" r:id="rId4"/>
+    <sheet name="البصريات" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase">'البصريات'!$A$1:$F$182</definedName>
+    <definedName name="_xlnm._FilterDatabase">البصريات!$A$1:$F$182</definedName>
   </definedNames>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="640">
   <si>
     <t>اسم المريض</t>
   </si>
@@ -1942,35 +1954,38 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFF"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
+      <sz val="8"/>
       <color theme="1"/>
-      <sz val="8"/>
       <name val="Tajawal"/>
     </font>
     <font>
+      <sz val="7"/>
       <color theme="1"/>
-      <sz val="7"/>
       <name val="Tajawal"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1979,7 +1994,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="1F4E78"/>
+        <fgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
     <fill>
@@ -1990,12 +2005,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="DDEBF7"/>
+        <fgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="E4DFEC"/>
+        <fgColor rgb="FFE4DFEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2009,16 +2030,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="B4C6E7"/>
+        <color rgb="FFB4C6E7"/>
       </left>
       <right style="thin">
-        <color rgb="B4C6E7"/>
+        <color rgb="FFB4C6E7"/>
       </right>
       <top style="thin">
-        <color rgb="B4C6E7"/>
+        <color rgb="FFB4C6E7"/>
       </top>
       <bottom style="thin">
-        <color rgb="B4C6E7"/>
+        <color rgb="FFB4C6E7"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2026,7 +2047,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
@@ -2040,6 +2061,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2378,9 +2402,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G184"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -2390,7 +2414,7 @@
     <col min="6" max="7" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6218,8 +6242,8 @@
       <c r="D160">
         <v>500</v>
       </c>
-      <c r="E160" t="s">
-        <v>547</v>
+      <c r="E160" s="7">
+        <v>46171</v>
       </c>
       <c r="F160" t="s">
         <v>557</v>
@@ -6804,8 +6828,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G184"/>
+  <autoFilter ref="A1:G184" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>